--- a/Tables/aov_fitness_all_table_GlucoseQuantity.xlsx
+++ b/Tables/aov_fitness_all_table_GlucoseQuantity.xlsx
@@ -394,17 +394,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1.190</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.465</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.094</t>
         </is>
       </c>
     </row>
@@ -421,7 +421,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>51.852</t>
+          <t>46.782</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -443,17 +443,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.020</t>
+          <t>2.955</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.931</t>
+          <t>8.726</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.004</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.867</t>
+          <t>37.931</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -492,17 +492,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>2.285</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.032</t>
+          <t>3.131</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>74.749</t>
+          <t>81.742</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
